--- a/data/trans_dic/IQ2608_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ2608_R3-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82,52%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76,41%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>55,27%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>83,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>78,85%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>61,94%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,36; 61,97</t>
+          <t>53,05; 65,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,58; 87,83</t>
+          <t>76,54; 87,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 84,34</t>
+          <t>84,03; 92,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,14; 75,08</t>
+          <t>60,74; 86,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,62; 65,08</t>
+          <t>48,12; 62,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,66; 87,02</t>
+          <t>76,91; 88,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,96; 93,46</t>
+          <t>72,55; 84,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,02; 86,44</t>
+          <t>45,94; 74,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,69; 61,98</t>
+          <t>52,11; 62,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,11; 86,32</t>
+          <t>78,73; 86,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80,28; 87,54</t>
+          <t>80,58; 87,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 78,81</t>
+          <t>58,15; 78,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>56,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>82,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>81,47%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>61,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,62; 61,57</t>
+          <t>56,09; 67,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,76; 86,04</t>
+          <t>80,62; 88,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,65; 85,18</t>
+          <t>77,94; 86,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,18; 85,83</t>
+          <t>69,5; 87,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,59; 66,95</t>
+          <t>50,56; 61,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,43; 88,5</t>
+          <t>77,56; 85,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,94; 85,92</t>
+          <t>76,74; 84,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,82; 88,69</t>
+          <t>62,11; 86,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,51; 63,25</t>
+          <t>55,61; 63,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80,28; 86,34</t>
+          <t>80,61; 86,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,61; 84,64</t>
+          <t>78,88; 84,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,46; 85,09</t>
+          <t>70,68; 85,15</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75,99%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>75,92%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>90,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,0; 68,31</t>
+          <t>56,88; 69,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,09; 80,79</t>
+          <t>70,57; 81,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,14; 93,55</t>
+          <t>81,0; 90,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,69; 75,0</t>
+          <t>39,49; 67,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,15; 69,83</t>
+          <t>55,55; 68,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,98; 80,57</t>
+          <t>69,92; 81,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,72; 89,81</t>
+          <t>85,98; 93,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,55; 68,65</t>
+          <t>37,07; 67,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,95; 67,09</t>
+          <t>58,17; 66,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,81; 79,57</t>
+          <t>72,01; 79,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,76; 90,55</t>
+          <t>85,13; 90,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,08; 67,41</t>
+          <t>43,85; 64,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>67,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>81,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,46%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62,77%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,09; 72,24</t>
+          <t>62,84; 73,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,95; 86,34</t>
+          <t>77,42; 86,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,85; 78,34</t>
+          <t>72,98; 82,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,88; 73,41</t>
+          <t>45,89; 72,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,03; 73,36</t>
+          <t>61,94; 73,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,78; 86,59</t>
+          <t>76,78; 86,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,62; 82,16</t>
+          <t>68,33; 78,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,15; 74,07</t>
+          <t>47,69; 72,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,74; 71,75</t>
+          <t>63,56; 71,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78,76; 85,22</t>
+          <t>78,57; 85,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,01; 78,98</t>
+          <t>71,91; 78,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,29; 71,0</t>
+          <t>51,25; 68,65</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,48</t>
+          <t>60,47; 66,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,45; 83,3</t>
+          <t>79,41; 83,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,81</t>
+          <t>80,85; 85,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58,15; 71,23</t>
+          <t>61,81; 74,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,82; 66,59</t>
+          <t>57,64; 63,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,33; 84,15</t>
+          <t>78,13; 83,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,0; 85,6</t>
+          <t>77,95; 82,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,76; 75,49</t>
+          <t>56,85; 70,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,12; 64,28</t>
+          <t>59,9; 64,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,59; 83,12</t>
+          <t>79,62; 83,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,54</t>
+          <t>80,34; 83,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,92; 72,15</t>
+          <t>61,44; 70,9</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87501</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122134</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>131589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>74065</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>114547</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>103416</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16844</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87501</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>122134</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>131589</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27198</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>41817</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64804; 83049</t>
+          <t>78425; 97466</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107055; 121197</t>
+          <t>113282; 129359</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94873; 110620</t>
+          <t>123790; 136923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12820; 20418</t>
+          <t>19724; 28165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77780; 96210</t>
+          <t>64481; 83598</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>113465; 128799</t>
+          <t>106126; 121480</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>125159; 137677</t>
+          <t>95161; 110633</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22204; 30455</t>
+          <t>12743; 20535</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>148493; 174694</t>
+          <t>146865; 174956</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>226249; 246875</t>
+          <t>225173; 246023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223563; 243790</t>
+          <t>224400; 244444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37052; 49197</t>
+          <t>35013; 47225</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>251</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129848</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184890</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>182601</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46798</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>108604</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>163243</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>166833</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29505</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>129848</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>184890</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>182601</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>30014</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79842</t>
+          <t>76813</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97540; 118647</t>
+          <t>117573; 141454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154471; 170919</t>
+          <t>175525; 192950</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>156971; 174449</t>
+          <t>172872; 191230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24446; 33742</t>
+          <t>40860; 51296</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>118618; 140325</t>
+          <t>97417; 118942</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>175122; 192690</t>
+          <t>154074; 170419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>172858; 190565</t>
+          <t>157162; 173589</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43655; 55452</t>
+          <t>24448; 33875</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223300; 254437</t>
+          <t>223695; 254145</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>334282; 359479</t>
+          <t>335636; 359613</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>335335; 361053</t>
+          <t>336495; 361581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71751; 86650</t>
+          <t>69377; 83577</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90702</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120380</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142359</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22699</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>81566</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>114238</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>137791</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17766</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90702</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>120380</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>142359</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>37400</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72391; 89902</t>
+          <t>81556; 99855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>105463; 121557</t>
+          <t>111792; 128483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131749; 143073</t>
+          <t>134067; 149193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12900; 22666</t>
+          <t>16391; 27970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81943; 100116</t>
+          <t>73111; 89909</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110854; 127635</t>
+          <t>105208; 122094</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>133600; 148641</t>
+          <t>131509; 142988</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17918; 30334</t>
+          <t>10112; 18465</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159371; 184482</t>
+          <t>159969; 183607</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221793; 245778</t>
+          <t>222421; 246194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269923; 288360</t>
+          <t>271101; 289329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34286; 50156</t>
+          <t>30163; 44367</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141460</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166816</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>157248</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27647</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>138439</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>165703</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>150328</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29103</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>141460</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>166816</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>157248</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59943</t>
+          <t>55033</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126049; 149070</t>
+          <t>129736; 151857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155917; 174935</t>
+          <t>156354; 174999</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138862; 160317</t>
+          <t>147947; 166782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23127; 34035</t>
+          <t>20923; 33238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130141; 151460</t>
+          <t>127815; 151309</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>157068; 174864</t>
+          <t>155569; 174673</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>147211; 166557</t>
+          <t>139842; 160340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23995; 36906</t>
+          <t>21537; 32590</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>263110; 296210</t>
+          <t>262374; 293506</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>318637; 344771</t>
+          <t>317844; 345528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293353; 321724</t>
+          <t>292945; 321629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51264; 68296</t>
+          <t>46511; 62304</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>801</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>449512</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594219</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>449512</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>594219</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>382463; 421897</t>
+          <t>427713; 469268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>541099; 574532</t>
+          <t>576562; 609777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>541123; 574331</t>
+          <t>596134; 629014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83202; 101927</t>
+          <t>110250; 133410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>430161; 470967</t>
+          <t>383130; 422022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>575995; 611031</t>
+          <t>538893; 573373</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>597211; 631168</t>
+          <t>540588; 573493</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120350; 144765</t>
+          <t>79324; 97910</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>824752; 881865</t>
+          <t>821846; 881029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1126863; 1176791</t>
+          <t>1127254; 1176340</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1148659; 1195316</t>
+          <t>1149605; 1195652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>210701; 241588</t>
+          <t>195323; 225383</t>
         </is>
       </c>
     </row>
